--- a/tests/TC-18/results/teacher_timetables_even.xlsx
+++ b/tests/TC-18/results/teacher_timetables_even.xlsx
@@ -55,14 +55,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00BBDEFB"/>
-        <bgColor rgb="00BBDEFB"/>
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
+        <fgColor rgb="00BBDEFB"/>
+        <bgColor rgb="00BBDEFB"/>
       </patternFill>
     </fill>
   </fills>
@@ -616,19 +616,37 @@
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr"/>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>MA163 TUT
-(CSE_2_B)
-Room: C004</t>
-        </is>
-      </c>
+      <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="3" t="inlineStr"/>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr"/>
-      <c r="I3" s="3" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(CSE_2_B)
+Room: C004</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(CSE_2_B)
+Room: C004</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(CSE_2_B)
+Room: C004</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(CSE_2_B)
+Room: C004</t>
+        </is>
+      </c>
       <c r="J3" s="3" t="inlineStr"/>
       <c r="K3" s="3" t="inlineStr"/>
       <c r="L3" s="3" t="inlineStr"/>
@@ -636,16 +654,28 @@
       <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="3" t="inlineStr"/>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="4" t="inlineStr">
-        <is>
-          <t>MA163 TUT
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
 (ECE_2)
-Room: 102</t>
-        </is>
-      </c>
+Room: C004</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(ECE_2)
+Room: C004</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(ECE_2)
+Room: C004</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr"/>
     </row>
     <row r="4" ht="35" customHeight="1">
@@ -656,34 +686,10 @@
       </c>
       <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>MA163 LEC
-(CSE_2_B)
-Room: C004</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>MA163 LEC
-(CSE_2_B)
-Room: C004</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>MA163 LEC
-(CSE_2_B)
-Room: C004</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>MA163 LEC
-(CSE_2_B)
-Room: C004</t>
-        </is>
-      </c>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr"/>
       <c r="H4" s="5" t="inlineStr"/>
       <c r="I4" s="5" t="inlineStr"/>
       <c r="J4" s="5" t="inlineStr"/>
@@ -692,9 +698,27 @@
       <c r="M4" s="5" t="inlineStr"/>
       <c r="N4" s="5" t="inlineStr"/>
       <c r="O4" s="5" t="inlineStr"/>
-      <c r="P4" s="5" t="inlineStr"/>
-      <c r="Q4" s="5" t="inlineStr"/>
-      <c r="R4" s="5" t="inlineStr"/>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(ECE_2)
+Room: C004</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(ECE_2)
+Room: C004</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(ECE_2)
+Room: C004</t>
+        </is>
+      </c>
       <c r="S4" s="5" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
@@ -718,9 +742,27 @@
       <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr"/>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>MA163 TUT
+(CSE_2_B)
+Room: C004</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>MA163 TUT
+(CSE_2_B)
+Room: C004</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>MA163 TUT
+(CSE_2_B)
+Room: C004</t>
+        </is>
+      </c>
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr"/>
       <c r="T5" s="3" t="inlineStr"/>
@@ -734,53 +776,53 @@
       </c>
       <c r="B6" s="5" t="inlineStr"/>
       <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>MA163 LEC
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(CSE_2_B)
+Room: C004</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(CSE_2_B)
+Room: C004</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(CSE_2_B)
+Room: C004</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>MA163 LEC
+(CSE_2_B)
+Room: C004</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="6" t="inlineStr">
+        <is>
+          <t>MA163 TUT
 (ECE_2)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="H6" s="6" t="inlineStr">
-        <is>
-          <t>MA163 LEC
+Room: C004</t>
+        </is>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>MA163 TUT
 (ECE_2)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>MA163 LEC
-(ECE_2)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
-        <is>
-          <t>MA163 LEC
-(ECE_2)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="inlineStr"/>
+Room: C004</t>
+        </is>
+      </c>
       <c r="L6" s="5" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr">
-        <is>
-          <t>MA163 LEC
-(CSE_2_B)
-Room: C004</t>
-        </is>
-      </c>
-      <c r="N6" s="6" t="inlineStr">
-        <is>
-          <t>MA163 LEC
-(CSE_2_B)
-Room: C004</t>
-        </is>
-      </c>
+      <c r="M6" s="5" t="inlineStr"/>
+      <c r="N6" s="5" t="inlineStr"/>
       <c r="O6" s="5" t="inlineStr"/>
       <c r="P6" s="5" t="inlineStr"/>
       <c r="Q6" s="5" t="inlineStr"/>
@@ -806,20 +848,8 @@
       <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr"/>
       <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>MA163 LEC
-(ECE_2)
-Room: 102</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>MA163 LEC
-(ECE_2)
-Room: 102</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr"/>
